--- a/MonthTemplate.xlsx
+++ b/MonthTemplate.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agecareltd.sharepoint.com/sites/NationalOperations/Shared Documents/Data summer (Felipe - Sunny)/Sundeep/Code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_A6BB9FE39BE7AC713C2B95966D8C47A52612C36B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB5DFB3D-0C2C-4FE4-904B-EB2850CA5F2C}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_A6BB9FE39BE7AC713C2B95966D8C47A52612C36B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D740620-BD31-4288-8000-2A96DFC74EB6}"/>
   <bookViews>
-    <workbookView xWindow="10920" yWindow="2145" windowWidth="30885" windowHeight="18300" tabRatio="692" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="692" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MonthYY" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -45,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="142">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -258,9 +271,6 @@
   </si>
   <si>
     <t xml:space="preserve"> Supplies (not funded)</t>
-  </si>
-  <si>
-    <t>BOTH R&amp;M (for ACIL)</t>
   </si>
   <si>
     <t>Budget</t>
@@ -726,7 +736,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -750,9 +760,6 @@
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1273,11 +1280,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BH88"/>
+  <dimension ref="A1:BH87"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.7109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="63.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.42578125" style="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="49.5703125" style="3" customWidth="1"/>
     <col min="5" max="5" width="22" style="3" bestFit="1" customWidth="1"/>
@@ -1347,166 +1354,166 @@
     </row>
     <row r="2" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="42" t="s">
+      <c r="F2" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="42" t="s">
+      <c r="H2" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="L2" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="M2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="N2" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="O2" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="20" t="s">
+      <c r="P2" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="20" t="s">
+      <c r="Q2" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="R2" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="20" t="s">
+      <c r="S2" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="T2" s="20" t="s">
+      <c r="T2" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="U2" s="20" t="s">
+      <c r="U2" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="V2" s="20" t="s">
+      <c r="V2" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="W2" s="20" t="s">
+      <c r="W2" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="X2" s="20" t="s">
+      <c r="X2" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Y2" s="20" t="s">
+      <c r="Y2" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="Z2" s="20" t="s">
+      <c r="Z2" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="AA2" s="20" t="s">
+      <c r="AA2" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="AB2" s="20" t="s">
+      <c r="AB2" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="AC2" s="20" t="s">
+      <c r="AC2" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="AD2" s="20" t="s">
+      <c r="AD2" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="AE2" s="20" t="s">
+      <c r="AE2" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="AF2" s="20" t="s">
+      <c r="AF2" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="AG2" s="20" t="s">
+      <c r="AG2" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="AH2" s="20" t="s">
+      <c r="AH2" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="AI2" s="20" t="s">
+      <c r="AI2" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="AJ2" s="20" t="s">
+      <c r="AJ2" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="AK2" s="20" t="s">
+      <c r="AK2" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="AL2" s="20" t="s">
+      <c r="AL2" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="AM2" s="20" t="s">
+      <c r="AM2" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="AN2" s="20" t="s">
+      <c r="AN2" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="AO2" s="20" t="s">
+      <c r="AO2" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="AP2" s="20" t="s">
+      <c r="AP2" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="AQ2" s="20" t="s">
+      <c r="AQ2" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="AR2" s="20" t="s">
+      <c r="AR2" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="AS2" s="20" t="s">
+      <c r="AS2" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="AT2" s="20" t="s">
+      <c r="AT2" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="AU2" s="20" t="s">
+      <c r="AU2" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AV2" s="20" t="s">
+      <c r="AV2" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="AW2" s="20" t="s">
+      <c r="AW2" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="AX2" s="20" t="s">
+      <c r="AX2" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="AY2" s="20" t="s">
+      <c r="AY2" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AZ2" s="20" t="s">
+      <c r="AZ2" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="BA2" s="20" t="s">
+      <c r="BA2" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="BB2" s="20" t="s">
+      <c r="BB2" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="BC2" s="20" t="s">
+      <c r="BC2" s="19" t="s">
         <v>56</v>
       </c>
       <c r="BE2" s="4" t="s">
@@ -1522,7 +1529,7 @@
     </row>
     <row r="3" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="42" t="s">
         <v>60</v>
       </c>
       <c r="C3" s="7"/>
@@ -1583,7 +1590,7 @@
     </row>
     <row r="4" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="42" t="s">
         <v>61</v>
       </c>
       <c r="C4" s="7"/>
@@ -1644,25 +1651,25 @@
     </row>
     <row r="5" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="11"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="10"/>
       <c r="I5" s="7"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44"/>
-      <c r="R5" s="44"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="43"/>
       <c r="S5" s="8"/>
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
@@ -1705,7 +1712,7 @@
     </row>
     <row r="6" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="42" t="s">
         <v>63</v>
       </c>
       <c r="C6" s="7"/>
@@ -1766,25 +1773,25 @@
     </row>
     <row r="7" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
       <c r="S7" s="8"/>
       <c r="T7" s="8"/>
       <c r="U7" s="8"/>
@@ -1818,7 +1825,7 @@
       <c r="AW7" s="8"/>
       <c r="AX7" s="8"/>
       <c r="AY7" s="8"/>
-      <c r="BA7" s="12"/>
+      <c r="BA7" s="11"/>
       <c r="BB7" s="9"/>
       <c r="BC7" s="9"/>
       <c r="BE7" s="7"/>
@@ -1827,25 +1834,25 @@
     </row>
     <row r="8" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="11"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="10"/>
       <c r="I8" s="7"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
       <c r="S8" s="8"/>
       <c r="T8" s="8"/>
       <c r="U8" s="8"/>
@@ -1879,7 +1886,7 @@
       <c r="AW8" s="8"/>
       <c r="AX8" s="8"/>
       <c r="AY8" s="8"/>
-      <c r="BA8" s="12"/>
+      <c r="BA8" s="11"/>
       <c r="BB8" s="9"/>
       <c r="BC8" s="9"/>
       <c r="BE8" s="7"/>
@@ -1888,25 +1895,25 @@
     </row>
     <row r="9" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
       <c r="S9" s="8"/>
       <c r="T9" s="8"/>
       <c r="U9" s="8"/>
@@ -1940,7 +1947,7 @@
       <c r="AW9" s="8"/>
       <c r="AX9" s="8"/>
       <c r="AY9" s="8"/>
-      <c r="BA9" s="12"/>
+      <c r="BA9" s="11"/>
       <c r="BB9" s="9"/>
       <c r="BC9" s="9"/>
       <c r="BE9" s="7"/>
@@ -1948,10 +1955,10 @@
       <c r="BH9" s="7"/>
     </row>
     <row r="10" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="42" t="s">
         <v>68</v>
       </c>
       <c r="C10" s="6"/>
@@ -1960,60 +1967,60 @@
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="47"/>
-      <c r="L10" s="47"/>
-      <c r="M10" s="47"/>
-      <c r="N10" s="47"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="47"/>
-      <c r="Q10" s="47"/>
-      <c r="R10" s="47"/>
-      <c r="S10" s="47"/>
-      <c r="T10" s="47"/>
-      <c r="U10" s="47"/>
-      <c r="V10" s="47"/>
-      <c r="W10" s="47"/>
-      <c r="X10" s="47"/>
-      <c r="Y10" s="47"/>
-      <c r="Z10" s="47"/>
-      <c r="AA10" s="47"/>
-      <c r="AB10" s="47"/>
-      <c r="AC10" s="47"/>
-      <c r="AD10" s="47"/>
-      <c r="AE10" s="47"/>
-      <c r="AF10" s="47"/>
-      <c r="AG10" s="47"/>
-      <c r="AH10" s="47"/>
-      <c r="AI10" s="47"/>
-      <c r="AJ10" s="47"/>
-      <c r="AK10" s="47"/>
-      <c r="AL10" s="47"/>
-      <c r="AM10" s="47"/>
-      <c r="AN10" s="47"/>
-      <c r="AO10" s="47"/>
-      <c r="AP10" s="47"/>
-      <c r="AQ10" s="47"/>
-      <c r="AR10" s="47"/>
-      <c r="AS10" s="47"/>
-      <c r="AT10" s="47"/>
-      <c r="AU10" s="47"/>
-      <c r="AV10" s="47"/>
-      <c r="AW10" s="47"/>
-      <c r="AX10" s="47"/>
-      <c r="AY10" s="47"/>
-      <c r="BA10" s="12"/>
-      <c r="BB10" s="47"/>
-      <c r="BC10" s="47"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="46"/>
+      <c r="K10" s="46"/>
+      <c r="L10" s="46"/>
+      <c r="M10" s="46"/>
+      <c r="N10" s="46"/>
+      <c r="O10" s="46"/>
+      <c r="P10" s="46"/>
+      <c r="Q10" s="46"/>
+      <c r="R10" s="46"/>
+      <c r="S10" s="46"/>
+      <c r="T10" s="46"/>
+      <c r="U10" s="46"/>
+      <c r="V10" s="46"/>
+      <c r="W10" s="46"/>
+      <c r="X10" s="46"/>
+      <c r="Y10" s="46"/>
+      <c r="Z10" s="46"/>
+      <c r="AA10" s="46"/>
+      <c r="AB10" s="46"/>
+      <c r="AC10" s="46"/>
+      <c r="AD10" s="46"/>
+      <c r="AE10" s="46"/>
+      <c r="AF10" s="46"/>
+      <c r="AG10" s="46"/>
+      <c r="AH10" s="46"/>
+      <c r="AI10" s="46"/>
+      <c r="AJ10" s="46"/>
+      <c r="AK10" s="46"/>
+      <c r="AL10" s="46"/>
+      <c r="AM10" s="46"/>
+      <c r="AN10" s="46"/>
+      <c r="AO10" s="46"/>
+      <c r="AP10" s="46"/>
+      <c r="AQ10" s="46"/>
+      <c r="AR10" s="46"/>
+      <c r="AS10" s="46"/>
+      <c r="AT10" s="46"/>
+      <c r="AU10" s="46"/>
+      <c r="AV10" s="46"/>
+      <c r="AW10" s="46"/>
+      <c r="AX10" s="46"/>
+      <c r="AY10" s="46"/>
+      <c r="BA10" s="11"/>
+      <c r="BB10" s="46"/>
+      <c r="BC10" s="46"/>
       <c r="BE10" s="7"/>
       <c r="BG10" s="7"/>
     </row>
     <row r="11" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="44" t="s">
         <v>70</v>
       </c>
       <c r="C11" s="7"/>
@@ -2065,7 +2072,7 @@
       <c r="AW11" s="9"/>
       <c r="AX11" s="9"/>
       <c r="AY11" s="9"/>
-      <c r="BA11" s="12"/>
+      <c r="BA11" s="11"/>
       <c r="BB11" s="9"/>
       <c r="BC11" s="9"/>
       <c r="BE11" s="7"/>
@@ -2074,265 +2081,257 @@
       <c r="B12" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
-      <c r="U12" s="10"/>
-      <c r="V12" s="10"/>
-      <c r="W12" s="10"/>
-      <c r="X12" s="10"/>
-      <c r="Y12" s="10"/>
-      <c r="Z12" s="10"/>
-      <c r="AA12" s="10"/>
-      <c r="AB12" s="10"/>
-      <c r="AC12" s="10"/>
-      <c r="AD12" s="10"/>
-      <c r="AE12" s="10"/>
-      <c r="AF12" s="10"/>
-      <c r="AG12" s="10"/>
-      <c r="AH12" s="10"/>
-      <c r="AI12" s="10"/>
-      <c r="AJ12" s="10"/>
-      <c r="AK12" s="10"/>
-      <c r="AL12" s="10"/>
-      <c r="AM12" s="10"/>
-      <c r="AN12" s="10"/>
-      <c r="AO12" s="10"/>
-      <c r="AP12" s="10"/>
-      <c r="AQ12" s="10"/>
-      <c r="AR12" s="10"/>
-      <c r="AS12" s="10"/>
-      <c r="AT12" s="10"/>
-      <c r="AU12" s="10"/>
-      <c r="AV12" s="10"/>
-      <c r="AW12" s="10"/>
-      <c r="AX12" s="10"/>
-      <c r="AY12" s="10"/>
-      <c r="AZ12" s="10"/>
-      <c r="BA12" s="10"/>
-      <c r="BB12" s="10"/>
-      <c r="BC12" s="10"/>
-      <c r="BE12" s="7"/>
-      <c r="BG12" s="7"/>
-      <c r="BH12" s="7"/>
+      <c r="C12" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="S12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="T12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="U12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="V12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="W12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="X12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AQ12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AR12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AS12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AT12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AU12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AV12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AW12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AX12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AY12" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AZ12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BA12" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="BB12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="BC12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="BE12" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG12" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH12" s="4" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="13" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B13" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="O13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="R13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="S13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="T13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="U13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="V13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="W13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="X13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AE13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="AG13" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="AH13" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI13" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ13" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AK13" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AN13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AO13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AP13" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AQ13" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AR13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AS13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AT13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AU13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AV13" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AW13" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AX13" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AY13" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AZ13" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="BA13" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="BB13" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="BC13" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="BE13" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="BG13" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH13" s="4" t="s">
-        <v>59</v>
-      </c>
+      <c r="B13" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="48"/>
+      <c r="M13" s="48"/>
+      <c r="N13" s="48"/>
+      <c r="O13" s="48"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="48"/>
+      <c r="R13" s="48"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="10"/>
+      <c r="Z13" s="10"/>
+      <c r="AA13" s="10"/>
+      <c r="AB13" s="10"/>
+      <c r="AC13" s="10"/>
+      <c r="AD13" s="10"/>
+      <c r="AE13" s="10"/>
+      <c r="AF13" s="10"/>
+      <c r="AG13" s="10"/>
+      <c r="AH13" s="9"/>
+      <c r="AI13" s="9"/>
+      <c r="AJ13" s="9"/>
+      <c r="AK13" s="9"/>
+      <c r="AL13" s="9"/>
+      <c r="AM13" s="9"/>
+      <c r="AN13" s="9"/>
+      <c r="AO13" s="9"/>
+      <c r="AP13" s="9"/>
+      <c r="AQ13" s="9"/>
+      <c r="AR13" s="9"/>
+      <c r="AS13" s="9"/>
+      <c r="AT13" s="9"/>
+      <c r="AU13" s="9"/>
+      <c r="AV13" s="9"/>
+      <c r="AW13" s="9"/>
+      <c r="AX13" s="9"/>
+      <c r="AY13" s="9"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="9"/>
+      <c r="BC13" s="9"/>
+      <c r="BE13" s="7"/>
     </row>
     <row r="14" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B14" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="I14" s="12"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="49"/>
-      <c r="L14" s="49"/>
-      <c r="M14" s="49"/>
-      <c r="N14" s="49"/>
-      <c r="O14" s="49"/>
-      <c r="P14" s="49"/>
-      <c r="Q14" s="49"/>
-      <c r="R14" s="49"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="11"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11"/>
-      <c r="Y14" s="11"/>
-      <c r="Z14" s="11"/>
-      <c r="AA14" s="11"/>
-      <c r="AB14" s="11"/>
-      <c r="AC14" s="11"/>
-      <c r="AD14" s="11"/>
-      <c r="AE14" s="11"/>
-      <c r="AF14" s="11"/>
-      <c r="AG14" s="11"/>
+      <c r="B14" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="48"/>
+      <c r="N14" s="48"/>
+      <c r="O14" s="48"/>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="48"/>
+      <c r="R14" s="48"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
+      <c r="Z14" s="10"/>
+      <c r="AA14" s="10"/>
+      <c r="AB14" s="10"/>
+      <c r="AC14" s="10"/>
+      <c r="AD14" s="10"/>
+      <c r="AE14" s="10"/>
+      <c r="AF14" s="10"/>
+      <c r="AG14" s="10"/>
       <c r="AH14" s="9"/>
       <c r="AI14" s="9"/>
       <c r="AJ14" s="9"/>
@@ -2351,41 +2350,46 @@
       <c r="AW14" s="9"/>
       <c r="AX14" s="9"/>
       <c r="AY14" s="9"/>
-      <c r="AZ14" s="13"/>
-      <c r="BA14" s="13"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
       <c r="BB14" s="9"/>
       <c r="BC14" s="9"/>
       <c r="BE14" s="7"/>
     </row>
     <row r="15" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B15" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="I15" s="12"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="49"/>
-      <c r="L15" s="49"/>
-      <c r="M15" s="49"/>
-      <c r="N15" s="49"/>
-      <c r="O15" s="49"/>
-      <c r="P15" s="49"/>
-      <c r="Q15" s="49"/>
-      <c r="R15" s="49"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="11"/>
-      <c r="W15" s="11"/>
-      <c r="X15" s="11"/>
-      <c r="Y15" s="11"/>
-      <c r="Z15" s="11"/>
-      <c r="AA15" s="11"/>
-      <c r="AB15" s="11"/>
-      <c r="AC15" s="11"/>
-      <c r="AD15" s="11"/>
-      <c r="AE15" s="11"/>
-      <c r="AF15" s="11"/>
-      <c r="AG15" s="11"/>
+      <c r="A15" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="48"/>
+      <c r="M15" s="48"/>
+      <c r="N15" s="48"/>
+      <c r="O15" s="48"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="48"/>
+      <c r="R15" s="48"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="10"/>
+      <c r="X15" s="10"/>
+      <c r="Y15" s="10"/>
+      <c r="Z15" s="10"/>
+      <c r="AA15" s="10"/>
+      <c r="AB15" s="10"/>
+      <c r="AC15" s="10"/>
+      <c r="AD15" s="10"/>
+      <c r="AE15" s="10"/>
+      <c r="AF15" s="10"/>
+      <c r="AG15" s="10"/>
       <c r="AH15" s="9"/>
       <c r="AI15" s="9"/>
       <c r="AJ15" s="9"/>
@@ -2404,46 +2408,45 @@
       <c r="AW15" s="9"/>
       <c r="AX15" s="9"/>
       <c r="AY15" s="9"/>
-      <c r="AZ15" s="13"/>
-      <c r="BA15" s="13"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
       <c r="BB15" s="9"/>
       <c r="BC15" s="9"/>
       <c r="BE15" s="7"/>
     </row>
     <row r="16" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="49"/>
-      <c r="K16" s="49"/>
-      <c r="L16" s="49"/>
-      <c r="M16" s="49"/>
-      <c r="N16" s="49"/>
-      <c r="O16" s="49"/>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="49"/>
-      <c r="R16" s="49"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="11"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11"/>
-      <c r="Y16" s="11"/>
-      <c r="Z16" s="11"/>
-      <c r="AA16" s="11"/>
-      <c r="AB16" s="11"/>
-      <c r="AC16" s="11"/>
-      <c r="AD16" s="11"/>
-      <c r="AE16" s="11"/>
-      <c r="AF16" s="11"/>
-      <c r="AG16" s="11"/>
+      <c r="B16" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="48"/>
+      <c r="K16" s="48"/>
+      <c r="L16" s="48"/>
+      <c r="M16" s="48"/>
+      <c r="N16" s="48"/>
+      <c r="O16" s="48"/>
+      <c r="P16" s="48"/>
+      <c r="Q16" s="48"/>
+      <c r="R16" s="48"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="10"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="10"/>
+      <c r="Z16" s="10"/>
+      <c r="AA16" s="10"/>
+      <c r="AB16" s="10"/>
+      <c r="AC16" s="10"/>
+      <c r="AD16" s="10"/>
+      <c r="AE16" s="10"/>
+      <c r="AF16" s="10"/>
+      <c r="AG16" s="10"/>
       <c r="AH16" s="9"/>
       <c r="AI16" s="9"/>
       <c r="AJ16" s="9"/>
@@ -2462,45 +2465,47 @@
       <c r="AW16" s="9"/>
       <c r="AX16" s="9"/>
       <c r="AY16" s="9"/>
-      <c r="AZ16" s="13"/>
-      <c r="BA16" s="13"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
       <c r="BB16" s="9"/>
       <c r="BC16" s="9"/>
       <c r="BE16" s="7"/>
     </row>
     <row r="17" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B17" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="49"/>
-      <c r="K17" s="49"/>
-      <c r="L17" s="49"/>
-      <c r="M17" s="49"/>
-      <c r="N17" s="49"/>
-      <c r="O17" s="49"/>
-      <c r="P17" s="49"/>
-      <c r="Q17" s="49"/>
-      <c r="R17" s="49"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="11"/>
-      <c r="W17" s="11"/>
-      <c r="X17" s="11"/>
-      <c r="Y17" s="11"/>
-      <c r="Z17" s="11"/>
-      <c r="AA17" s="11"/>
-      <c r="AB17" s="11"/>
-      <c r="AC17" s="11"/>
-      <c r="AD17" s="11"/>
-      <c r="AE17" s="11"/>
-      <c r="AF17" s="11"/>
-      <c r="AG17" s="11"/>
+      <c r="B17" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="48"/>
+      <c r="L17" s="48"/>
+      <c r="M17" s="48"/>
+      <c r="N17" s="48"/>
+      <c r="O17" s="48"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="48"/>
+      <c r="R17" s="48"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
+      <c r="V17" s="10"/>
+      <c r="W17" s="10"/>
+      <c r="X17" s="10"/>
+      <c r="Y17" s="10"/>
+      <c r="Z17" s="10"/>
+      <c r="AA17" s="10"/>
+      <c r="AB17" s="10"/>
+      <c r="AC17" s="10"/>
+      <c r="AD17" s="10"/>
+      <c r="AE17" s="10"/>
+      <c r="AF17" s="10"/>
+      <c r="AG17" s="10"/>
       <c r="AH17" s="9"/>
       <c r="AI17" s="9"/>
       <c r="AJ17" s="9"/>
@@ -2524,42 +2529,45 @@
       <c r="BB17" s="9"/>
       <c r="BC17" s="9"/>
       <c r="BE17" s="7"/>
+      <c r="BF17" s="7"/>
+      <c r="BG17" s="2"/>
+      <c r="BH17" s="2"/>
     </row>
     <row r="18" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="49"/>
-      <c r="K18" s="49"/>
-      <c r="L18" s="49"/>
-      <c r="M18" s="49"/>
-      <c r="N18" s="49"/>
-      <c r="O18" s="49"/>
-      <c r="P18" s="49"/>
-      <c r="Q18" s="49"/>
-      <c r="R18" s="49"/>
-      <c r="S18" s="11"/>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="11"/>
-      <c r="W18" s="11"/>
-      <c r="X18" s="11"/>
-      <c r="Y18" s="11"/>
-      <c r="Z18" s="11"/>
-      <c r="AA18" s="11"/>
-      <c r="AB18" s="11"/>
-      <c r="AC18" s="11"/>
-      <c r="AD18" s="11"/>
-      <c r="AE18" s="11"/>
-      <c r="AF18" s="11"/>
-      <c r="AG18" s="11"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="48"/>
+      <c r="M18" s="48"/>
+      <c r="N18" s="48"/>
+      <c r="O18" s="48"/>
+      <c r="P18" s="48"/>
+      <c r="Q18" s="48"/>
+      <c r="R18" s="48"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="X18" s="10"/>
+      <c r="Y18" s="10"/>
+      <c r="Z18" s="10"/>
+      <c r="AA18" s="10"/>
+      <c r="AB18" s="10"/>
+      <c r="AC18" s="10"/>
+      <c r="AD18" s="10"/>
+      <c r="AE18" s="10"/>
+      <c r="AF18" s="10"/>
+      <c r="AG18" s="10"/>
       <c r="AH18" s="9"/>
       <c r="AI18" s="9"/>
       <c r="AJ18" s="9"/>
@@ -2578,53 +2586,51 @@
       <c r="AW18" s="9"/>
       <c r="AX18" s="9"/>
       <c r="AY18" s="9"/>
-      <c r="AZ18" s="14"/>
-      <c r="BA18" s="14"/>
+      <c r="AZ18" s="13"/>
+      <c r="BA18" s="13"/>
       <c r="BB18" s="9"/>
       <c r="BC18" s="9"/>
       <c r="BE18" s="7"/>
-      <c r="BF18" s="7"/>
-      <c r="BG18" s="2"/>
-      <c r="BH18" s="2"/>
+      <c r="BF18" s="18"/>
     </row>
     <row r="19" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B19" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="49"/>
-      <c r="M19" s="49"/>
-      <c r="N19" s="49"/>
-      <c r="O19" s="49"/>
-      <c r="P19" s="49"/>
-      <c r="Q19" s="49"/>
-      <c r="R19" s="49"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="11"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="11"/>
-      <c r="Z19" s="11"/>
-      <c r="AA19" s="11"/>
-      <c r="AB19" s="11"/>
-      <c r="AC19" s="11"/>
-      <c r="AD19" s="11"/>
-      <c r="AE19" s="11"/>
-      <c r="AF19" s="11"/>
-      <c r="AG19" s="11"/>
+      <c r="B19" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
+      <c r="Z19" s="7"/>
+      <c r="AA19" s="7"/>
+      <c r="AB19" s="7"/>
+      <c r="AC19" s="7"/>
+      <c r="AD19" s="7"/>
+      <c r="AE19" s="7"/>
+      <c r="AF19" s="7"/>
+      <c r="AG19" s="7"/>
       <c r="AH19" s="9"/>
       <c r="AI19" s="9"/>
-      <c r="AJ19" s="9"/>
+      <c r="AJ19" s="39"/>
       <c r="AK19" s="9"/>
       <c r="AL19" s="9"/>
       <c r="AM19" s="9"/>
@@ -2640,51 +2646,48 @@
       <c r="AW19" s="9"/>
       <c r="AX19" s="9"/>
       <c r="AY19" s="9"/>
-      <c r="AZ19" s="14"/>
-      <c r="BA19" s="14"/>
+      <c r="AZ19" s="13"/>
+      <c r="BA19" s="9"/>
       <c r="BB19" s="9"/>
       <c r="BC19" s="9"/>
       <c r="BE19" s="7"/>
-      <c r="BF19" s="19"/>
+      <c r="BF19" s="18"/>
     </row>
     <row r="20" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B20" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
-      <c r="V20" s="7"/>
-      <c r="W20" s="7"/>
-      <c r="X20" s="7"/>
-      <c r="Y20" s="7"/>
-      <c r="Z20" s="7"/>
-      <c r="AA20" s="7"/>
-      <c r="AB20" s="7"/>
-      <c r="AC20" s="7"/>
-      <c r="AD20" s="7"/>
-      <c r="AE20" s="7"/>
-      <c r="AF20" s="7"/>
-      <c r="AG20" s="7"/>
+      <c r="A20" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I20" s="47"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+      <c r="S20" s="13"/>
+      <c r="T20" s="13"/>
+      <c r="U20" s="13"/>
+      <c r="V20" s="13"/>
+      <c r="W20" s="13"/>
+      <c r="X20" s="13"/>
+      <c r="Y20" s="13"/>
+      <c r="Z20" s="13"/>
+      <c r="AA20" s="13"/>
+      <c r="AB20" s="13"/>
+      <c r="AC20" s="13"/>
+      <c r="AD20" s="13"/>
+      <c r="AE20" s="13"/>
+      <c r="AF20" s="13"/>
+      <c r="AG20" s="13"/>
       <c r="AH20" s="9"/>
       <c r="AI20" s="9"/>
-      <c r="AJ20" s="40"/>
+      <c r="AJ20" s="9"/>
       <c r="AK20" s="9"/>
       <c r="AL20" s="9"/>
       <c r="AM20" s="9"/>
@@ -2700,295 +2703,301 @@
       <c r="AW20" s="9"/>
       <c r="AX20" s="9"/>
       <c r="AY20" s="9"/>
-      <c r="AZ20" s="14"/>
-      <c r="BA20" s="9"/>
+      <c r="AZ20" s="13"/>
+      <c r="BA20" s="13"/>
       <c r="BB20" s="9"/>
       <c r="BC20" s="9"/>
       <c r="BE20" s="7"/>
-      <c r="BF20" s="19"/>
+      <c r="BF20" s="18"/>
     </row>
     <row r="21" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B21" s="15" t="s">
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="13"/>
+      <c r="U21" s="13"/>
+      <c r="V21" s="13"/>
+      <c r="W21" s="13"/>
+      <c r="X21" s="13"/>
+      <c r="Y21" s="13"/>
+      <c r="Z21" s="13"/>
+      <c r="AA21" s="13"/>
+      <c r="AB21" s="13"/>
+      <c r="AC21" s="13"/>
+      <c r="AD21" s="13"/>
+      <c r="AE21" s="13"/>
+      <c r="AF21" s="13"/>
+      <c r="AG21" s="13"/>
+      <c r="AH21" s="13"/>
+      <c r="AI21" s="13"/>
+      <c r="AJ21" s="13"/>
+      <c r="AK21" s="13"/>
+      <c r="AL21" s="13"/>
+      <c r="AM21" s="13"/>
+      <c r="AN21" s="13"/>
+      <c r="AO21" s="13"/>
+      <c r="AP21" s="13"/>
+      <c r="AQ21" s="13"/>
+      <c r="AR21" s="13"/>
+      <c r="AS21" s="13"/>
+      <c r="AT21" s="13"/>
+      <c r="AU21" s="13"/>
+      <c r="AV21" s="13"/>
+      <c r="AW21" s="13"/>
+      <c r="AX21" s="13"/>
+      <c r="AY21" s="13"/>
+      <c r="AZ21" s="13"/>
+      <c r="BA21" s="13"/>
+      <c r="BB21" s="13"/>
+      <c r="BC21" s="13"/>
+      <c r="BE21" s="7"/>
+    </row>
+    <row r="22" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="B22" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="I21" s="48"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="14"/>
-      <c r="S21" s="14"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="14"/>
-      <c r="V21" s="14"/>
-      <c r="W21" s="14"/>
-      <c r="X21" s="14"/>
-      <c r="Y21" s="14"/>
-      <c r="Z21" s="14"/>
-      <c r="AA21" s="14"/>
-      <c r="AB21" s="14"/>
-      <c r="AC21" s="14"/>
-      <c r="AD21" s="14"/>
-      <c r="AE21" s="14"/>
-      <c r="AF21" s="14"/>
-      <c r="AG21" s="14"/>
-      <c r="AH21" s="9"/>
-      <c r="AI21" s="9"/>
-      <c r="AJ21" s="9"/>
-      <c r="AK21" s="9"/>
-      <c r="AL21" s="9"/>
-      <c r="AM21" s="9"/>
-      <c r="AN21" s="9"/>
-      <c r="AO21" s="9"/>
-      <c r="AP21" s="9"/>
-      <c r="AQ21" s="9"/>
-      <c r="AR21" s="9"/>
-      <c r="AS21" s="9"/>
-      <c r="AT21" s="9"/>
-      <c r="AU21" s="9"/>
-      <c r="AV21" s="9"/>
-      <c r="AW21" s="9"/>
-      <c r="AX21" s="9"/>
-      <c r="AY21" s="9"/>
-      <c r="AZ21" s="14"/>
-      <c r="BA21" s="14"/>
-      <c r="BB21" s="9"/>
-      <c r="BC21" s="9"/>
-      <c r="BE21" s="7"/>
-      <c r="BF21" s="19"/>
-    </row>
-    <row r="22" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="14"/>
-      <c r="S22" s="14"/>
-      <c r="T22" s="14"/>
-      <c r="U22" s="14"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="14"/>
-      <c r="X22" s="14"/>
-      <c r="Y22" s="14"/>
-      <c r="Z22" s="14"/>
-      <c r="AA22" s="14"/>
-      <c r="AB22" s="14"/>
-      <c r="AC22" s="14"/>
-      <c r="AD22" s="14"/>
-      <c r="AE22" s="14"/>
-      <c r="AF22" s="14"/>
-      <c r="AG22" s="14"/>
-      <c r="AH22" s="14"/>
-      <c r="AI22" s="14"/>
-      <c r="AJ22" s="14"/>
-      <c r="AK22" s="14"/>
-      <c r="AL22" s="14"/>
-      <c r="AM22" s="14"/>
-      <c r="AN22" s="14"/>
-      <c r="AO22" s="14"/>
-      <c r="AP22" s="14"/>
-      <c r="AQ22" s="14"/>
-      <c r="AR22" s="14"/>
-      <c r="AS22" s="14"/>
-      <c r="AT22" s="14"/>
-      <c r="AU22" s="14"/>
-      <c r="AV22" s="14"/>
-      <c r="AW22" s="14"/>
-      <c r="AX22" s="14"/>
-      <c r="AY22" s="14"/>
-      <c r="AZ22" s="14"/>
-      <c r="BA22" s="14"/>
-      <c r="BB22" s="14"/>
-      <c r="BC22" s="14"/>
-      <c r="BE22" s="7"/>
+      <c r="C22" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="P22" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="S22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="T22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="U22" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="V22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="W22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="X22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA22" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB22" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD22" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH22" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI22" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN22" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP22" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AQ22" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AR22" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AS22" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AT22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AU22" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AV22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AW22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AX22" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AY22" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AZ22" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BA22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="BB22" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="BC22" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="BE22" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG22" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH22" s="4" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="23" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B23" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="O23" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="P23" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q23" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="R23" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="S23" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="T23" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="U23" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="V23" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="W23" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="X23" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z23" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA23" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB23" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC23" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD23" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AE23" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF23" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="AG23" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="AH23" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI23" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ23" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AK23" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL23" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM23" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AN23" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AO23" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AP23" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AQ23" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AR23" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AS23" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AT23" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AU23" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AV23" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AW23" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AX23" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AY23" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AZ23" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="BA23" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="BB23" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="BC23" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="BE23" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="BG23" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH23" s="4" t="s">
-        <v>59</v>
-      </c>
+      <c r="B23" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7"/>
+      <c r="X23" s="7"/>
+      <c r="Y23" s="7"/>
+      <c r="Z23" s="7"/>
+      <c r="AA23" s="7"/>
+      <c r="AB23" s="7"/>
+      <c r="AC23" s="7"/>
+      <c r="AD23" s="7"/>
+      <c r="AE23" s="7"/>
+      <c r="AF23" s="7"/>
+      <c r="AG23" s="7"/>
+      <c r="AH23" s="7"/>
+      <c r="AI23" s="7"/>
+      <c r="AJ23" s="7"/>
+      <c r="AK23" s="7"/>
+      <c r="AL23" s="7"/>
+      <c r="AM23" s="7"/>
+      <c r="AN23" s="7"/>
+      <c r="AO23" s="7"/>
+      <c r="AP23" s="7"/>
+      <c r="AQ23" s="7"/>
+      <c r="AR23" s="7"/>
+      <c r="AS23" s="7"/>
+      <c r="AT23" s="7"/>
+      <c r="AU23" s="7"/>
+      <c r="AV23" s="7"/>
+      <c r="AW23" s="7"/>
+      <c r="AX23" s="7"/>
+      <c r="AY23" s="7"/>
+      <c r="AZ23" s="7"/>
+      <c r="BA23" s="7"/>
+      <c r="BB23" s="7"/>
+      <c r="BC23" s="7"/>
+      <c r="BD23" s="7"/>
+      <c r="BE23" s="7"/>
+      <c r="BF23" s="7"/>
+      <c r="BG23" s="7"/>
+      <c r="BH23" s="7"/>
     </row>
     <row r="24" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B24" s="15" t="s">
-        <v>60</v>
+      <c r="B24" s="14" t="s">
+        <v>61</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
@@ -3050,8 +3059,8 @@
       <c r="BH24" s="7"/>
     </row>
     <row r="25" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B25" s="15" t="s">
-        <v>61</v>
+      <c r="B25" s="14" t="s">
+        <v>72</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -3113,15 +3122,15 @@
       <c r="BH25" s="7"/>
     </row>
     <row r="26" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B26" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
+      <c r="B26" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
@@ -3176,15 +3185,15 @@
       <c r="BH26" s="7"/>
     </row>
     <row r="27" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B27" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
+      <c r="B27" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
@@ -3239,8 +3248,8 @@
       <c r="BH27" s="7"/>
     </row>
     <row r="28" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B28" s="15" t="s">
-        <v>78</v>
+      <c r="B28" s="14" t="s">
+        <v>65</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -3302,8 +3311,8 @@
       <c r="BH28" s="7"/>
     </row>
     <row r="29" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B29" s="15" t="s">
-        <v>65</v>
+      <c r="B29" s="14" t="s">
+        <v>66</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -3360,13 +3369,10 @@
       <c r="BC29" s="7"/>
       <c r="BD29" s="7"/>
       <c r="BE29" s="7"/>
-      <c r="BF29" s="7"/>
-      <c r="BG29" s="7"/>
-      <c r="BH29" s="7"/>
     </row>
     <row r="30" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B30" s="15" t="s">
-        <v>66</v>
+      <c r="B30" s="14" t="s">
+        <v>75</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -3421,1319 +3427,1259 @@
       <c r="BA30" s="7"/>
       <c r="BB30" s="7"/>
       <c r="BC30" s="7"/>
-      <c r="BD30" s="7"/>
+      <c r="BD30" s="26"/>
       <c r="BE30" s="7"/>
     </row>
     <row r="31" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B31" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7"/>
-      <c r="P31" s="7"/>
-      <c r="Q31" s="7"/>
-      <c r="R31" s="7"/>
-      <c r="S31" s="7"/>
-      <c r="T31" s="7"/>
-      <c r="U31" s="7"/>
-      <c r="V31" s="7"/>
-      <c r="W31" s="7"/>
-      <c r="X31" s="7"/>
-      <c r="Y31" s="7"/>
-      <c r="Z31" s="7"/>
-      <c r="AA31" s="7"/>
-      <c r="AB31" s="7"/>
-      <c r="AC31" s="7"/>
-      <c r="AD31" s="7"/>
-      <c r="AE31" s="7"/>
-      <c r="AF31" s="7"/>
-      <c r="AG31" s="7"/>
-      <c r="AH31" s="7"/>
-      <c r="AI31" s="7"/>
-      <c r="AJ31" s="7"/>
-      <c r="AK31" s="7"/>
-      <c r="AL31" s="7"/>
-      <c r="AM31" s="7"/>
-      <c r="AN31" s="7"/>
-      <c r="AO31" s="7"/>
-      <c r="AP31" s="7"/>
-      <c r="AQ31" s="7"/>
-      <c r="AR31" s="7"/>
-      <c r="AS31" s="7"/>
-      <c r="AT31" s="7"/>
-      <c r="AU31" s="7"/>
-      <c r="AV31" s="7"/>
-      <c r="AW31" s="7"/>
-      <c r="AX31" s="7"/>
-      <c r="AY31" s="7"/>
-      <c r="AZ31" s="7"/>
-      <c r="BA31" s="7"/>
-      <c r="BB31" s="7"/>
-      <c r="BC31" s="7"/>
-      <c r="BD31" s="27"/>
-      <c r="BE31" s="7"/>
+      <c r="I31" s="16"/>
+      <c r="AH31" s="16"/>
+      <c r="AI31" s="16"/>
+      <c r="AJ31" s="16"/>
+      <c r="AK31" s="16"/>
+      <c r="AL31" s="16"/>
+      <c r="AM31" s="16"/>
+      <c r="AN31" s="16"/>
+      <c r="AO31" s="16"/>
+      <c r="AP31" s="16"/>
+      <c r="AQ31" s="16"/>
+      <c r="AR31" s="16"/>
+      <c r="AS31" s="16"/>
+      <c r="AT31" s="16"/>
+      <c r="AU31" s="16"/>
+      <c r="AV31" s="16"/>
+      <c r="AW31" s="16"/>
+      <c r="AX31" s="16"/>
+      <c r="AY31" s="16"/>
+      <c r="AZ31" s="16"/>
+      <c r="BA31" s="16"/>
+      <c r="BB31" s="16"/>
+      <c r="BC31" s="16"/>
     </row>
     <row r="32" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="I32" s="17"/>
-      <c r="AH32" s="17"/>
-      <c r="AI32" s="17"/>
-      <c r="AJ32" s="17"/>
-      <c r="AK32" s="17"/>
-      <c r="AL32" s="17"/>
-      <c r="AM32" s="17"/>
-      <c r="AN32" s="17"/>
-      <c r="AO32" s="17"/>
-      <c r="AP32" s="17"/>
-      <c r="AQ32" s="17"/>
-      <c r="AR32" s="17"/>
-      <c r="AS32" s="17"/>
-      <c r="AT32" s="17"/>
-      <c r="AU32" s="17"/>
-      <c r="AV32" s="17"/>
-      <c r="AW32" s="17"/>
-      <c r="AX32" s="17"/>
-      <c r="AY32" s="17"/>
-      <c r="AZ32" s="17"/>
-      <c r="BA32" s="17"/>
-      <c r="BB32" s="17"/>
-      <c r="BC32" s="17"/>
-    </row>
-    <row r="33" spans="2:60" x14ac:dyDescent="0.25">
-      <c r="B33" s="16" t="s">
+      <c r="B32" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="O32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="P32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q32" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="R32" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="S32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="T32" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="U32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="V32" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="W32" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="X32" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y32" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z32" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA32" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB32" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC32" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD32" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE32" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF32" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH32" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI32" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ32" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK32" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM32" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN32" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO32" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP32" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AQ32" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AR32" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AS32" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AT32" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AU32" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AV32" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AW32" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AX32" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AY32" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AZ32" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BA32" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="BB32" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="BC32" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="BE32" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG32" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH32" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="B33" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13"/>
+      <c r="P33" s="13"/>
+      <c r="Q33" s="13"/>
+      <c r="R33" s="13"/>
+      <c r="S33" s="13"/>
+      <c r="T33" s="13"/>
+      <c r="U33" s="13"/>
+      <c r="V33" s="13"/>
+      <c r="W33" s="13"/>
+      <c r="X33" s="13"/>
+      <c r="Y33" s="13"/>
+      <c r="Z33" s="13"/>
+      <c r="AA33" s="13"/>
+      <c r="AB33" s="13"/>
+      <c r="AC33" s="13"/>
+      <c r="AD33" s="13"/>
+      <c r="AE33" s="13"/>
+      <c r="AF33" s="13"/>
+      <c r="AG33" s="13"/>
+      <c r="AH33" s="13"/>
+      <c r="AI33" s="13"/>
+      <c r="AJ33" s="13"/>
+      <c r="AK33" s="13"/>
+      <c r="AL33" s="13"/>
+      <c r="AM33" s="13"/>
+      <c r="AN33" s="13"/>
+      <c r="AO33" s="13"/>
+      <c r="AP33" s="13"/>
+      <c r="AQ33" s="13"/>
+      <c r="AR33" s="13"/>
+      <c r="AS33" s="13"/>
+      <c r="AT33" s="13"/>
+      <c r="AU33" s="13"/>
+      <c r="AV33" s="13"/>
+      <c r="AW33" s="13"/>
+      <c r="AX33" s="13"/>
+      <c r="AY33" s="13"/>
+      <c r="AZ33" s="13"/>
+      <c r="BA33" s="13"/>
+      <c r="BB33" s="13"/>
+      <c r="BC33" s="13"/>
+      <c r="BD33" s="13"/>
+      <c r="BE33" s="13"/>
+    </row>
+    <row r="34" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="B34" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13"/>
+      <c r="P34" s="13"/>
+      <c r="Q34" s="13"/>
+      <c r="R34" s="13"/>
+      <c r="S34" s="13"/>
+      <c r="T34" s="13"/>
+      <c r="U34" s="13"/>
+      <c r="V34" s="13"/>
+      <c r="W34" s="13"/>
+      <c r="X34" s="13"/>
+      <c r="Y34" s="13"/>
+      <c r="Z34" s="13"/>
+      <c r="AA34" s="13"/>
+      <c r="AB34" s="13"/>
+      <c r="AC34" s="13"/>
+      <c r="AD34" s="13"/>
+      <c r="AE34" s="13"/>
+      <c r="AF34" s="13"/>
+      <c r="AG34" s="13"/>
+      <c r="AH34" s="13"/>
+      <c r="AI34" s="13"/>
+      <c r="AJ34" s="13"/>
+      <c r="AK34" s="13"/>
+      <c r="AL34" s="13"/>
+      <c r="AM34" s="13"/>
+      <c r="AN34" s="13"/>
+      <c r="AO34" s="13"/>
+      <c r="AP34" s="13"/>
+      <c r="AQ34" s="13"/>
+      <c r="AR34" s="13"/>
+      <c r="AS34" s="13"/>
+      <c r="AT34" s="13"/>
+      <c r="AU34" s="13"/>
+      <c r="AV34" s="13"/>
+      <c r="AW34" s="13"/>
+      <c r="AX34" s="13"/>
+      <c r="AY34" s="13"/>
+      <c r="AZ34" s="13"/>
+      <c r="BA34" s="13"/>
+      <c r="BB34" s="13"/>
+      <c r="BC34" s="13"/>
+      <c r="BD34" s="13"/>
+      <c r="BE34" s="13"/>
+    </row>
+    <row r="35" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="B35" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13"/>
+      <c r="P35" s="13"/>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="13"/>
+      <c r="S35" s="13"/>
+      <c r="T35" s="13"/>
+      <c r="U35" s="13"/>
+      <c r="V35" s="13"/>
+      <c r="W35" s="13"/>
+      <c r="X35" s="13"/>
+      <c r="Y35" s="13"/>
+      <c r="Z35" s="13"/>
+      <c r="AA35" s="13"/>
+      <c r="AB35" s="13"/>
+      <c r="AC35" s="13"/>
+      <c r="AD35" s="13"/>
+      <c r="AE35" s="13"/>
+      <c r="AF35" s="13"/>
+      <c r="AG35" s="13"/>
+      <c r="AH35" s="13"/>
+      <c r="AI35" s="13"/>
+      <c r="AJ35" s="13"/>
+      <c r="AK35" s="13"/>
+      <c r="AL35" s="13"/>
+      <c r="AM35" s="13"/>
+      <c r="AN35" s="13"/>
+      <c r="AO35" s="13"/>
+      <c r="AP35" s="13"/>
+      <c r="AQ35" s="13"/>
+      <c r="AR35" s="13"/>
+      <c r="AS35" s="13"/>
+      <c r="AT35" s="13"/>
+      <c r="AU35" s="13"/>
+      <c r="AV35" s="13"/>
+      <c r="AW35" s="13"/>
+      <c r="AX35" s="13"/>
+      <c r="AY35" s="13"/>
+      <c r="AZ35" s="13"/>
+      <c r="BA35" s="13"/>
+      <c r="BB35" s="13"/>
+      <c r="BC35" s="13"/>
+      <c r="BD35" s="13"/>
+      <c r="BE35" s="13"/>
+    </row>
+    <row r="36" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="B36" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L33" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="M33" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N33" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="O33" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="P33" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q33" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="R33" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="S33" s="4" t="s">
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13"/>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="13"/>
+      <c r="S36" s="13"/>
+      <c r="T36" s="13"/>
+      <c r="U36" s="13"/>
+      <c r="V36" s="13"/>
+      <c r="W36" s="13"/>
+      <c r="X36" s="13"/>
+      <c r="Y36" s="13"/>
+      <c r="Z36" s="13"/>
+      <c r="AA36" s="13"/>
+      <c r="AB36" s="13"/>
+      <c r="AC36" s="13"/>
+      <c r="AD36" s="13"/>
+      <c r="AE36" s="13"/>
+      <c r="AF36" s="13"/>
+      <c r="AG36" s="13"/>
+      <c r="AH36" s="13"/>
+      <c r="AI36" s="13"/>
+      <c r="AJ36" s="13"/>
+      <c r="AK36" s="13"/>
+      <c r="AL36" s="13"/>
+      <c r="AM36" s="13"/>
+      <c r="AN36" s="13"/>
+      <c r="AO36" s="13"/>
+      <c r="AP36" s="13"/>
+      <c r="AQ36" s="13"/>
+      <c r="AR36" s="13"/>
+      <c r="AS36" s="13"/>
+      <c r="AT36" s="13"/>
+      <c r="AU36" s="13"/>
+      <c r="AV36" s="13"/>
+      <c r="AW36" s="13"/>
+      <c r="AX36" s="13"/>
+      <c r="AY36" s="13"/>
+      <c r="AZ36" s="13"/>
+      <c r="BA36" s="13"/>
+      <c r="BB36" s="13"/>
+      <c r="BC36" s="13"/>
+      <c r="BD36" s="13"/>
+      <c r="BE36" s="13"/>
+    </row>
+    <row r="37" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="B37" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13"/>
+      <c r="P37" s="13"/>
+      <c r="Q37" s="13"/>
+      <c r="R37" s="13"/>
+      <c r="S37" s="13"/>
+      <c r="T37" s="13"/>
+      <c r="U37" s="13"/>
+      <c r="V37" s="13"/>
+      <c r="W37" s="13"/>
+      <c r="X37" s="13"/>
+      <c r="Y37" s="13"/>
+      <c r="Z37" s="13"/>
+      <c r="AA37" s="13"/>
+      <c r="AB37" s="13"/>
+      <c r="AC37" s="13"/>
+      <c r="AD37" s="13"/>
+      <c r="AE37" s="13"/>
+      <c r="AF37" s="13"/>
+      <c r="AG37" s="13"/>
+      <c r="AH37" s="13"/>
+      <c r="AI37" s="13"/>
+      <c r="AJ37" s="13"/>
+      <c r="AK37" s="13"/>
+      <c r="AL37" s="13"/>
+      <c r="AM37" s="13"/>
+      <c r="AN37" s="13"/>
+      <c r="AO37" s="13"/>
+      <c r="AP37" s="13"/>
+      <c r="AQ37" s="13"/>
+      <c r="AR37" s="13"/>
+      <c r="AS37" s="13"/>
+      <c r="AT37" s="13"/>
+      <c r="AU37" s="13"/>
+      <c r="AV37" s="13"/>
+      <c r="AW37" s="13"/>
+      <c r="AX37" s="13"/>
+      <c r="AY37" s="13"/>
+      <c r="AZ37" s="13"/>
+      <c r="BA37" s="13"/>
+      <c r="BB37" s="13"/>
+      <c r="BC37" s="13"/>
+      <c r="BD37" s="13"/>
+      <c r="BE37" s="13"/>
+    </row>
+    <row r="38" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="B38" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13"/>
+      <c r="P38" s="13"/>
+      <c r="Q38" s="13"/>
+      <c r="R38" s="13"/>
+      <c r="S38" s="13"/>
+      <c r="T38" s="13"/>
+      <c r="U38" s="13"/>
+      <c r="V38" s="13"/>
+      <c r="W38" s="13"/>
+      <c r="X38" s="13"/>
+      <c r="Y38" s="13"/>
+      <c r="Z38" s="13"/>
+      <c r="AA38" s="13"/>
+      <c r="AB38" s="13"/>
+      <c r="AC38" s="13"/>
+      <c r="AD38" s="13"/>
+      <c r="AE38" s="13"/>
+      <c r="AF38" s="13"/>
+      <c r="AG38" s="13"/>
+      <c r="AH38" s="13"/>
+      <c r="AI38" s="13"/>
+      <c r="AJ38" s="13"/>
+      <c r="AK38" s="13"/>
+      <c r="AL38" s="13"/>
+      <c r="AM38" s="13"/>
+      <c r="AN38" s="13"/>
+      <c r="AO38" s="13"/>
+      <c r="AP38" s="13"/>
+      <c r="AQ38" s="13"/>
+      <c r="AR38" s="13"/>
+      <c r="AS38" s="13"/>
+      <c r="AT38" s="13"/>
+      <c r="AU38" s="13"/>
+      <c r="AV38" s="13"/>
+      <c r="AW38" s="13"/>
+      <c r="AX38" s="13"/>
+      <c r="AY38" s="13"/>
+      <c r="AZ38" s="13"/>
+      <c r="BA38" s="13"/>
+      <c r="BB38" s="13"/>
+      <c r="BC38" s="13"/>
+      <c r="BD38" s="13"/>
+      <c r="BE38" s="13"/>
+    </row>
+    <row r="39" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="B39" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13"/>
+      <c r="P39" s="13"/>
+      <c r="Q39" s="13"/>
+      <c r="R39" s="13"/>
+      <c r="S39" s="13"/>
+      <c r="T39" s="13"/>
+      <c r="U39" s="13"/>
+      <c r="V39" s="13"/>
+      <c r="W39" s="13"/>
+      <c r="X39" s="13"/>
+      <c r="Y39" s="13"/>
+      <c r="Z39" s="13"/>
+      <c r="AA39" s="13"/>
+      <c r="AB39" s="13"/>
+      <c r="AC39" s="13"/>
+      <c r="AD39" s="13"/>
+      <c r="AE39" s="13"/>
+      <c r="AF39" s="13"/>
+      <c r="AG39" s="13"/>
+      <c r="AH39" s="13"/>
+      <c r="AI39" s="13"/>
+      <c r="AJ39" s="13"/>
+      <c r="AK39" s="13"/>
+      <c r="AL39" s="13"/>
+      <c r="AM39" s="13"/>
+      <c r="AN39" s="13"/>
+      <c r="AO39" s="13"/>
+      <c r="AP39" s="13"/>
+      <c r="AQ39" s="13"/>
+      <c r="AR39" s="13"/>
+      <c r="AS39" s="13"/>
+      <c r="AT39" s="13"/>
+      <c r="AU39" s="13"/>
+      <c r="AV39" s="13"/>
+      <c r="AW39" s="13"/>
+      <c r="AX39" s="13"/>
+      <c r="AY39" s="13"/>
+      <c r="AZ39" s="13"/>
+      <c r="BA39" s="13"/>
+      <c r="BB39" s="13"/>
+      <c r="BC39" s="13"/>
+      <c r="BD39" s="13"/>
+      <c r="BE39" s="13"/>
+    </row>
+    <row r="40" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="D40" s="38"/>
+    </row>
+    <row r="41" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="D41" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="B42" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="22"/>
+      <c r="J42" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="B43" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="T33" s="4" t="s">
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="22"/>
+      <c r="J43" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="K43" s="23"/>
+      <c r="L43" s="23"/>
+      <c r="M43" s="16"/>
+    </row>
+    <row r="44" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="B44" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="U33" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="V33" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="W33" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="X33" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y33" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z33" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA33" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB33" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC33" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD33" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AE33" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF33" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="AG33" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="AH33" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI33" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ33" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AK33" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL33" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM33" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AN33" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AO33" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AP33" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AQ33" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AR33" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AS33" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AT33" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AU33" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AV33" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AW33" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AX33" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AY33" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AZ33" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="BA33" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="BB33" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="BC33" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="BE33" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="BG33" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH33" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="2:60" x14ac:dyDescent="0.25">
-      <c r="B34" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="14"/>
-      <c r="P34" s="14"/>
-      <c r="Q34" s="14"/>
-      <c r="R34" s="14"/>
-      <c r="S34" s="14"/>
-      <c r="T34" s="14"/>
-      <c r="U34" s="14"/>
-      <c r="V34" s="14"/>
-      <c r="W34" s="14"/>
-      <c r="X34" s="14"/>
-      <c r="Y34" s="14"/>
-      <c r="Z34" s="14"/>
-      <c r="AA34" s="14"/>
-      <c r="AB34" s="14"/>
-      <c r="AC34" s="14"/>
-      <c r="AD34" s="14"/>
-      <c r="AE34" s="14"/>
-      <c r="AF34" s="14"/>
-      <c r="AG34" s="14"/>
-      <c r="AH34" s="14"/>
-      <c r="AI34" s="14"/>
-      <c r="AJ34" s="14"/>
-      <c r="AK34" s="14"/>
-      <c r="AL34" s="14"/>
-      <c r="AM34" s="14"/>
-      <c r="AN34" s="14"/>
-      <c r="AO34" s="14"/>
-      <c r="AP34" s="14"/>
-      <c r="AQ34" s="14"/>
-      <c r="AR34" s="14"/>
-      <c r="AS34" s="14"/>
-      <c r="AT34" s="14"/>
-      <c r="AU34" s="14"/>
-      <c r="AV34" s="14"/>
-      <c r="AW34" s="14"/>
-      <c r="AX34" s="14"/>
-      <c r="AY34" s="14"/>
-      <c r="AZ34" s="14"/>
-      <c r="BA34" s="14"/>
-      <c r="BB34" s="14"/>
-      <c r="BC34" s="14"/>
-      <c r="BD34" s="14"/>
-      <c r="BE34" s="14"/>
-    </row>
-    <row r="35" spans="2:60" x14ac:dyDescent="0.25">
-      <c r="B35" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="14"/>
-      <c r="P35" s="14"/>
-      <c r="Q35" s="14"/>
-      <c r="R35" s="14"/>
-      <c r="S35" s="14"/>
-      <c r="T35" s="14"/>
-      <c r="U35" s="14"/>
-      <c r="V35" s="14"/>
-      <c r="W35" s="14"/>
-      <c r="X35" s="14"/>
-      <c r="Y35" s="14"/>
-      <c r="Z35" s="14"/>
-      <c r="AA35" s="14"/>
-      <c r="AB35" s="14"/>
-      <c r="AC35" s="14"/>
-      <c r="AD35" s="14"/>
-      <c r="AE35" s="14"/>
-      <c r="AF35" s="14"/>
-      <c r="AG35" s="14"/>
-      <c r="AH35" s="14"/>
-      <c r="AI35" s="14"/>
-      <c r="AJ35" s="14"/>
-      <c r="AK35" s="14"/>
-      <c r="AL35" s="14"/>
-      <c r="AM35" s="14"/>
-      <c r="AN35" s="14"/>
-      <c r="AO35" s="14"/>
-      <c r="AP35" s="14"/>
-      <c r="AQ35" s="14"/>
-      <c r="AR35" s="14"/>
-      <c r="AS35" s="14"/>
-      <c r="AT35" s="14"/>
-      <c r="AU35" s="14"/>
-      <c r="AV35" s="14"/>
-      <c r="AW35" s="14"/>
-      <c r="AX35" s="14"/>
-      <c r="AY35" s="14"/>
-      <c r="AZ35" s="14"/>
-      <c r="BA35" s="14"/>
-      <c r="BB35" s="14"/>
-      <c r="BC35" s="14"/>
-      <c r="BD35" s="14"/>
-      <c r="BE35" s="14"/>
-    </row>
-    <row r="36" spans="2:60" x14ac:dyDescent="0.25">
-      <c r="B36" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14"/>
-      <c r="P36" s="14"/>
-      <c r="Q36" s="14"/>
-      <c r="R36" s="14"/>
-      <c r="S36" s="14"/>
-      <c r="T36" s="14"/>
-      <c r="U36" s="14"/>
-      <c r="V36" s="14"/>
-      <c r="W36" s="14"/>
-      <c r="X36" s="14"/>
-      <c r="Y36" s="14"/>
-      <c r="Z36" s="14"/>
-      <c r="AA36" s="14"/>
-      <c r="AB36" s="14"/>
-      <c r="AC36" s="14"/>
-      <c r="AD36" s="14"/>
-      <c r="AE36" s="14"/>
-      <c r="AF36" s="14"/>
-      <c r="AG36" s="14"/>
-      <c r="AH36" s="14"/>
-      <c r="AI36" s="14"/>
-      <c r="AJ36" s="14"/>
-      <c r="AK36" s="14"/>
-      <c r="AL36" s="14"/>
-      <c r="AM36" s="14"/>
-      <c r="AN36" s="14"/>
-      <c r="AO36" s="14"/>
-      <c r="AP36" s="14"/>
-      <c r="AQ36" s="14"/>
-      <c r="AR36" s="14"/>
-      <c r="AS36" s="14"/>
-      <c r="AT36" s="14"/>
-      <c r="AU36" s="14"/>
-      <c r="AV36" s="14"/>
-      <c r="AW36" s="14"/>
-      <c r="AX36" s="14"/>
-      <c r="AY36" s="14"/>
-      <c r="AZ36" s="14"/>
-      <c r="BA36" s="14"/>
-      <c r="BB36" s="14"/>
-      <c r="BC36" s="14"/>
-      <c r="BD36" s="14"/>
-      <c r="BE36" s="14"/>
-    </row>
-    <row r="37" spans="2:60" x14ac:dyDescent="0.25">
-      <c r="B37" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
-      <c r="N37" s="14"/>
-      <c r="O37" s="14"/>
-      <c r="P37" s="14"/>
-      <c r="Q37" s="14"/>
-      <c r="R37" s="14"/>
-      <c r="S37" s="14"/>
-      <c r="T37" s="14"/>
-      <c r="U37" s="14"/>
-      <c r="V37" s="14"/>
-      <c r="W37" s="14"/>
-      <c r="X37" s="14"/>
-      <c r="Y37" s="14"/>
-      <c r="Z37" s="14"/>
-      <c r="AA37" s="14"/>
-      <c r="AB37" s="14"/>
-      <c r="AC37" s="14"/>
-      <c r="AD37" s="14"/>
-      <c r="AE37" s="14"/>
-      <c r="AF37" s="14"/>
-      <c r="AG37" s="14"/>
-      <c r="AH37" s="14"/>
-      <c r="AI37" s="14"/>
-      <c r="AJ37" s="14"/>
-      <c r="AK37" s="14"/>
-      <c r="AL37" s="14"/>
-      <c r="AM37" s="14"/>
-      <c r="AN37" s="14"/>
-      <c r="AO37" s="14"/>
-      <c r="AP37" s="14"/>
-      <c r="AQ37" s="14"/>
-      <c r="AR37" s="14"/>
-      <c r="AS37" s="14"/>
-      <c r="AT37" s="14"/>
-      <c r="AU37" s="14"/>
-      <c r="AV37" s="14"/>
-      <c r="AW37" s="14"/>
-      <c r="AX37" s="14"/>
-      <c r="AY37" s="14"/>
-      <c r="AZ37" s="14"/>
-      <c r="BA37" s="14"/>
-      <c r="BB37" s="14"/>
-      <c r="BC37" s="14"/>
-      <c r="BD37" s="14"/>
-      <c r="BE37" s="14"/>
-    </row>
-    <row r="38" spans="2:60" x14ac:dyDescent="0.25">
-      <c r="B38" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
-      <c r="K38" s="14"/>
-      <c r="L38" s="14"/>
-      <c r="M38" s="14"/>
-      <c r="N38" s="14"/>
-      <c r="O38" s="14"/>
-      <c r="P38" s="14"/>
-      <c r="Q38" s="14"/>
-      <c r="R38" s="14"/>
-      <c r="S38" s="14"/>
-      <c r="T38" s="14"/>
-      <c r="U38" s="14"/>
-      <c r="V38" s="14"/>
-      <c r="W38" s="14"/>
-      <c r="X38" s="14"/>
-      <c r="Y38" s="14"/>
-      <c r="Z38" s="14"/>
-      <c r="AA38" s="14"/>
-      <c r="AB38" s="14"/>
-      <c r="AC38" s="14"/>
-      <c r="AD38" s="14"/>
-      <c r="AE38" s="14"/>
-      <c r="AF38" s="14"/>
-      <c r="AG38" s="14"/>
-      <c r="AH38" s="14"/>
-      <c r="AI38" s="14"/>
-      <c r="AJ38" s="14"/>
-      <c r="AK38" s="14"/>
-      <c r="AL38" s="14"/>
-      <c r="AM38" s="14"/>
-      <c r="AN38" s="14"/>
-      <c r="AO38" s="14"/>
-      <c r="AP38" s="14"/>
-      <c r="AQ38" s="14"/>
-      <c r="AR38" s="14"/>
-      <c r="AS38" s="14"/>
-      <c r="AT38" s="14"/>
-      <c r="AU38" s="14"/>
-      <c r="AV38" s="14"/>
-      <c r="AW38" s="14"/>
-      <c r="AX38" s="14"/>
-      <c r="AY38" s="14"/>
-      <c r="AZ38" s="14"/>
-      <c r="BA38" s="14"/>
-      <c r="BB38" s="14"/>
-      <c r="BC38" s="14"/>
-      <c r="BD38" s="14"/>
-      <c r="BE38" s="14"/>
-    </row>
-    <row r="39" spans="2:60" x14ac:dyDescent="0.25">
-      <c r="B39" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14"/>
-      <c r="K39" s="14"/>
-      <c r="L39" s="14"/>
-      <c r="M39" s="14"/>
-      <c r="N39" s="14"/>
-      <c r="O39" s="14"/>
-      <c r="P39" s="14"/>
-      <c r="Q39" s="14"/>
-      <c r="R39" s="14"/>
-      <c r="S39" s="14"/>
-      <c r="T39" s="14"/>
-      <c r="U39" s="14"/>
-      <c r="V39" s="14"/>
-      <c r="W39" s="14"/>
-      <c r="X39" s="14"/>
-      <c r="Y39" s="14"/>
-      <c r="Z39" s="14"/>
-      <c r="AA39" s="14"/>
-      <c r="AB39" s="14"/>
-      <c r="AC39" s="14"/>
-      <c r="AD39" s="14"/>
-      <c r="AE39" s="14"/>
-      <c r="AF39" s="14"/>
-      <c r="AG39" s="14"/>
-      <c r="AH39" s="14"/>
-      <c r="AI39" s="14"/>
-      <c r="AJ39" s="14"/>
-      <c r="AK39" s="14"/>
-      <c r="AL39" s="14"/>
-      <c r="AM39" s="14"/>
-      <c r="AN39" s="14"/>
-      <c r="AO39" s="14"/>
-      <c r="AP39" s="14"/>
-      <c r="AQ39" s="14"/>
-      <c r="AR39" s="14"/>
-      <c r="AS39" s="14"/>
-      <c r="AT39" s="14"/>
-      <c r="AU39" s="14"/>
-      <c r="AV39" s="14"/>
-      <c r="AW39" s="14"/>
-      <c r="AX39" s="14"/>
-      <c r="AY39" s="14"/>
-      <c r="AZ39" s="14"/>
-      <c r="BA39" s="14"/>
-      <c r="BB39" s="14"/>
-      <c r="BC39" s="14"/>
-      <c r="BD39" s="14"/>
-      <c r="BE39" s="14"/>
-    </row>
-    <row r="40" spans="2:60" x14ac:dyDescent="0.25">
-      <c r="B40" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="14"/>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
-      <c r="M40" s="14"/>
-      <c r="N40" s="14"/>
-      <c r="O40" s="14"/>
-      <c r="P40" s="14"/>
-      <c r="Q40" s="14"/>
-      <c r="R40" s="14"/>
-      <c r="S40" s="14"/>
-      <c r="T40" s="14"/>
-      <c r="U40" s="14"/>
-      <c r="V40" s="14"/>
-      <c r="W40" s="14"/>
-      <c r="X40" s="14"/>
-      <c r="Y40" s="14"/>
-      <c r="Z40" s="14"/>
-      <c r="AA40" s="14"/>
-      <c r="AB40" s="14"/>
-      <c r="AC40" s="14"/>
-      <c r="AD40" s="14"/>
-      <c r="AE40" s="14"/>
-      <c r="AF40" s="14"/>
-      <c r="AG40" s="14"/>
-      <c r="AH40" s="14"/>
-      <c r="AI40" s="14"/>
-      <c r="AJ40" s="14"/>
-      <c r="AK40" s="14"/>
-      <c r="AL40" s="14"/>
-      <c r="AM40" s="14"/>
-      <c r="AN40" s="14"/>
-      <c r="AO40" s="14"/>
-      <c r="AP40" s="14"/>
-      <c r="AQ40" s="14"/>
-      <c r="AR40" s="14"/>
-      <c r="AS40" s="14"/>
-      <c r="AT40" s="14"/>
-      <c r="AU40" s="14"/>
-      <c r="AV40" s="14"/>
-      <c r="AW40" s="14"/>
-      <c r="AX40" s="14"/>
-      <c r="AY40" s="14"/>
-      <c r="AZ40" s="14"/>
-      <c r="BA40" s="14"/>
-      <c r="BB40" s="14"/>
-      <c r="BC40" s="14"/>
-      <c r="BD40" s="14"/>
-      <c r="BE40" s="14"/>
-    </row>
-    <row r="41" spans="2:60" x14ac:dyDescent="0.25">
-      <c r="D41" s="39"/>
-    </row>
-    <row r="42" spans="2:60" x14ac:dyDescent="0.25">
-      <c r="D42" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" spans="2:60" x14ac:dyDescent="0.25">
-      <c r="B43" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="23"/>
-      <c r="J43" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" spans="2:60" x14ac:dyDescent="0.25">
-      <c r="B44" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
-      <c r="F44" s="23"/>
+      <c r="F44" s="22"/>
       <c r="J44" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K44" s="24"/>
-      <c r="L44" s="24"/>
-      <c r="M44" s="17"/>
-    </row>
-    <row r="45" spans="2:60" x14ac:dyDescent="0.25">
-      <c r="B45" s="15" t="s">
         <v>92</v>
       </c>
+      <c r="K44" s="23"/>
+      <c r="L44" s="23"/>
+      <c r="M44" s="16"/>
+    </row>
+    <row r="45" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="B45" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="C45" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
-      <c r="F45" s="23"/>
+      <c r="F45" s="22"/>
       <c r="J45" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="K45" s="24"/>
-      <c r="L45" s="24"/>
-      <c r="M45" s="17"/>
-    </row>
-    <row r="46" spans="2:60" x14ac:dyDescent="0.25">
-      <c r="B46" s="15" t="s">
         <v>94</v>
       </c>
+      <c r="K45" s="23"/>
+      <c r="L45" s="23"/>
+      <c r="M45" s="16"/>
+    </row>
+    <row r="46" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="B46" s="14" t="s">
+        <v>95</v>
+      </c>
       <c r="C46" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
-      <c r="F46" s="23"/>
+      <c r="F46" s="22"/>
       <c r="J46" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="K46" s="24"/>
-      <c r="L46" s="24"/>
-      <c r="M46" s="17"/>
-    </row>
-    <row r="47" spans="2:60" x14ac:dyDescent="0.25">
-      <c r="B47" s="15" t="s">
         <v>96</v>
       </c>
+      <c r="K46" s="23"/>
+      <c r="L46" s="23"/>
+      <c r="M46" s="16"/>
+    </row>
+    <row r="47" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="B47" s="14" t="s">
+        <v>97</v>
+      </c>
       <c r="C47" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
-      <c r="F47" s="23"/>
+      <c r="F47" s="22"/>
       <c r="J47" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="K47" s="24"/>
-      <c r="L47" s="24"/>
-      <c r="M47" s="17"/>
-    </row>
-    <row r="48" spans="2:60" x14ac:dyDescent="0.25">
-      <c r="B48" s="15" t="s">
         <v>98</v>
       </c>
+      <c r="K47" s="23"/>
+      <c r="L47" s="23"/>
+      <c r="M47" s="16"/>
+    </row>
+    <row r="48" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="B48" s="14" t="s">
+        <v>99</v>
+      </c>
       <c r="C48" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
-      <c r="F48" s="23"/>
+      <c r="F48" s="22"/>
       <c r="J48" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="K48" s="24"/>
-      <c r="L48" s="24"/>
-      <c r="M48" s="17"/>
-    </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B49" s="15" t="s">
         <v>100</v>
       </c>
+      <c r="K48" s="23"/>
+      <c r="L48" s="23"/>
+      <c r="M48" s="16"/>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B49" s="14" t="s">
+        <v>101</v>
+      </c>
       <c r="C49" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
-      <c r="F49" s="23"/>
+      <c r="F49" s="22"/>
       <c r="J49" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K49" s="24"/>
-      <c r="L49" s="24"/>
-      <c r="M49" s="17"/>
-    </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B50" s="15" t="s">
         <v>102</v>
       </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B50" s="14" t="s">
+        <v>103</v>
+      </c>
       <c r="C50" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
-      <c r="F50" s="23"/>
-      <c r="J50" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B51" s="15" t="s">
+      <c r="F50" s="22"/>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B51" s="14" t="s">
         <v>104</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
-      <c r="F51" s="23"/>
-    </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B52" s="15" t="s">
+      <c r="F51" s="24"/>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B52" s="14" t="s">
         <v>105</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
-      <c r="F52" s="25"/>
-    </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B53" s="15" t="s">
+      <c r="F52" s="24"/>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B53" s="14" t="s">
         <v>106</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
-      <c r="F53" s="25"/>
-    </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B54" s="15" t="s">
+      <c r="F53" s="24"/>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B54" s="14" t="s">
         <v>107</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
-      <c r="F54" s="25"/>
-    </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B55" s="15" t="s">
+      <c r="F54" s="24"/>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B55" s="14" t="s">
         <v>108</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
-      <c r="F55" s="25"/>
-    </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B56" s="15" t="s">
+      <c r="F55" s="24"/>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B56" s="14" t="s">
         <v>109</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
-      <c r="F56" s="25"/>
-    </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B57" s="15" t="s">
+      <c r="F56" s="24"/>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B57" s="14" t="s">
         <v>110</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
-      <c r="F57" s="25"/>
-    </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="F57" s="24"/>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="25"/>
-    </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B59" s="16" t="s">
+      <c r="C58" s="4"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="22"/>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B59" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="C59" s="4"/>
+      <c r="C59" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="D59" s="26"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="23"/>
-    </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B60" s="15" t="s">
+      <c r="E59" s="7"/>
+      <c r="F59" s="22"/>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B60" s="14" t="s">
         <v>113</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D60" s="27"/>
+        <v>16</v>
+      </c>
+      <c r="D60" s="26"/>
       <c r="E60" s="7"/>
-      <c r="F60" s="23"/>
-    </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B61" s="15" t="s">
+      <c r="F60" s="22"/>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B61" s="14" t="s">
         <v>114</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D61" s="27"/>
+        <v>17</v>
+      </c>
+      <c r="D61" s="26"/>
       <c r="E61" s="7"/>
-      <c r="F61" s="23"/>
-    </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B62" s="15" t="s">
+      <c r="F61" s="22"/>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B62" s="14" t="s">
         <v>115</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D62" s="27"/>
+        <v>18</v>
+      </c>
+      <c r="D62" s="26"/>
       <c r="E62" s="7"/>
-      <c r="F62" s="23"/>
-    </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B63" s="15" t="s">
+      <c r="F62" s="22"/>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B63" s="14" t="s">
         <v>116</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D63" s="27"/>
+        <v>19</v>
+      </c>
+      <c r="D63" s="26"/>
       <c r="E63" s="7"/>
-      <c r="F63" s="23"/>
-    </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B64" s="15" t="s">
+      <c r="F63" s="22"/>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B64" s="14" t="s">
         <v>117</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D64" s="27"/>
+        <v>10</v>
+      </c>
+      <c r="D64" s="26"/>
       <c r="E64" s="7"/>
-      <c r="F64" s="23"/>
+      <c r="F64" s="22"/>
     </row>
     <row r="65" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="14" t="s">
         <v>118</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D65" s="27"/>
+        <v>11</v>
+      </c>
+      <c r="D65" s="26"/>
       <c r="E65" s="7"/>
-      <c r="F65" s="23"/>
+      <c r="F65" s="22"/>
     </row>
     <row r="66" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="14" t="s">
         <v>119</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D66" s="27"/>
+        <v>12</v>
+      </c>
+      <c r="D66" s="26"/>
       <c r="E66" s="7"/>
-      <c r="F66" s="23"/>
+      <c r="F66" s="22"/>
     </row>
     <row r="67" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B67" s="15" t="s">
+      <c r="B67" s="14" t="s">
         <v>120</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D67" s="27"/>
+        <v>13</v>
+      </c>
+      <c r="D67" s="26"/>
       <c r="E67" s="7"/>
-      <c r="F67" s="23"/>
+      <c r="F67" s="22"/>
     </row>
     <row r="68" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B68" s="15" t="s">
+      <c r="B68" s="14" t="s">
         <v>121</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D68" s="27"/>
+        <v>14</v>
+      </c>
+      <c r="D68" s="26"/>
       <c r="E68" s="7"/>
-      <c r="F68" s="23"/>
+      <c r="F68" s="22"/>
+      <c r="N68" s="27"/>
     </row>
     <row r="69" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D69" s="27"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="23"/>
-      <c r="N69" s="28"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="22"/>
     </row>
     <row r="70" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B70" s="16" t="s">
+      <c r="B70" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="23"/>
+      <c r="C70" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="22"/>
+      <c r="H70" s="28"/>
+      <c r="I70" s="29"/>
+      <c r="J70" s="22"/>
+      <c r="K70" s="22"/>
+      <c r="L70" s="22"/>
+      <c r="M70" s="22"/>
+      <c r="N70" s="22"/>
+      <c r="O70" s="22"/>
+      <c r="P70" s="22"/>
+      <c r="Q70" s="22"/>
     </row>
     <row r="71" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B71" s="38" t="s">
+      <c r="B71" s="37" t="s">
         <v>124</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D71" s="7"/>
       <c r="E71" s="7"/>
-      <c r="F71" s="23"/>
-      <c r="H71" s="29"/>
+      <c r="F71" s="22"/>
+      <c r="H71" s="28"/>
       <c r="I71" s="30"/>
-      <c r="J71" s="23"/>
-      <c r="K71" s="23"/>
-      <c r="L71" s="23"/>
-      <c r="M71" s="23"/>
-      <c r="N71" s="23"/>
-      <c r="O71" s="23"/>
-      <c r="P71" s="23"/>
-      <c r="Q71" s="23"/>
+      <c r="J71" s="31"/>
+      <c r="K71" s="31"/>
+      <c r="L71" s="31"/>
+      <c r="M71" s="31"/>
+      <c r="N71" s="31"/>
+      <c r="O71" s="31"/>
+      <c r="P71" s="31"/>
+      <c r="Q71" s="31"/>
     </row>
     <row r="72" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B72" s="38" t="s">
+      <c r="B72" s="37" t="s">
         <v>125</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D72" s="7"/>
       <c r="E72" s="7"/>
-      <c r="F72" s="23"/>
-      <c r="H72" s="29"/>
-      <c r="I72" s="31"/>
+      <c r="F72" s="22"/>
+      <c r="H72" s="28"/>
+      <c r="I72" s="30"/>
       <c r="J72" s="32"/>
-      <c r="K72" s="32"/>
-      <c r="L72" s="32"/>
-      <c r="M72" s="32"/>
-      <c r="N72" s="32"/>
-      <c r="O72" s="32"/>
-      <c r="P72" s="32"/>
-      <c r="Q72" s="32"/>
+      <c r="K72" s="31"/>
     </row>
     <row r="73" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B73" s="38" t="s">
+      <c r="B73" s="37" t="s">
         <v>126</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D73" s="7"/>
       <c r="E73" s="7"/>
-      <c r="F73" s="23"/>
-      <c r="H73" s="29"/>
-      <c r="I73" s="31"/>
-      <c r="J73" s="33"/>
-      <c r="K73" s="32"/>
+      <c r="F73" s="22"/>
+      <c r="H73" s="28"/>
+      <c r="I73" s="30"/>
+      <c r="J73" s="32"/>
+      <c r="K73" s="31"/>
     </row>
     <row r="74" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B74" s="38" t="s">
+      <c r="B74" s="37" t="s">
         <v>127</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D74" s="7"/>
       <c r="E74" s="7"/>
-      <c r="F74" s="23"/>
-      <c r="H74" s="29"/>
-      <c r="I74" s="31"/>
-      <c r="J74" s="33"/>
-      <c r="K74" s="32"/>
+      <c r="F74" s="22"/>
+      <c r="H74" s="28"/>
+      <c r="I74" s="30"/>
+      <c r="J74" s="32"/>
+      <c r="K74" s="31"/>
     </row>
     <row r="75" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B75" s="38" t="s">
+      <c r="B75" s="37" t="s">
         <v>128</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D75" s="7"/>
       <c r="E75" s="7"/>
-      <c r="F75" s="23"/>
-      <c r="H75" s="29"/>
-      <c r="I75" s="31"/>
-      <c r="J75" s="33"/>
-      <c r="K75" s="32"/>
+      <c r="F75" s="22"/>
+      <c r="H75" s="28"/>
+      <c r="I75" s="30"/>
+      <c r="J75" s="32"/>
+      <c r="K75" s="31"/>
     </row>
     <row r="76" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B76" s="38" t="s">
+      <c r="B76" s="37" t="s">
         <v>129</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D76" s="7"/>
       <c r="E76" s="7"/>
-      <c r="F76" s="23"/>
-      <c r="H76" s="29"/>
-      <c r="I76" s="31"/>
-      <c r="J76" s="33"/>
-      <c r="K76" s="32"/>
+      <c r="F76" s="22"/>
+      <c r="H76" s="28"/>
+      <c r="I76" s="30"/>
+      <c r="J76" s="32"/>
+      <c r="K76" s="31"/>
     </row>
     <row r="77" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B77" s="38" t="s">
+      <c r="B77" s="37" t="s">
         <v>130</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
-      <c r="F77" s="23"/>
-      <c r="H77" s="29"/>
-      <c r="I77" s="31"/>
-      <c r="J77" s="33"/>
-      <c r="K77" s="32"/>
+      <c r="F77" s="22"/>
+      <c r="H77" s="28"/>
+      <c r="I77" s="30"/>
+      <c r="J77" s="32"/>
+      <c r="K77" s="31"/>
     </row>
     <row r="78" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B78" s="38" t="s">
+      <c r="B78" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="C78" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D78" s="7"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="23"/>
-      <c r="H78" s="29"/>
-      <c r="I78" s="31"/>
-      <c r="J78" s="33"/>
-      <c r="K78" s="32"/>
+      <c r="D78" s="19"/>
+      <c r="E78" s="19"/>
+      <c r="F78" s="22"/>
+      <c r="H78" s="33"/>
+      <c r="I78" s="34"/>
+      <c r="J78" s="35"/>
+      <c r="K78" s="31"/>
     </row>
     <row r="79" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B79" s="16" t="s">
+      <c r="B79" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="D79" s="20"/>
-      <c r="E79" s="20"/>
-      <c r="F79" s="23"/>
-      <c r="H79" s="34"/>
-      <c r="I79" s="35"/>
-      <c r="J79" s="36"/>
-      <c r="K79" s="32"/>
+      <c r="C79" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="22"/>
+      <c r="H79" s="28"/>
+      <c r="I79" s="29"/>
+      <c r="J79" s="32"/>
+      <c r="K79" s="31"/>
     </row>
     <row r="80" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B80" s="38" t="s">
+      <c r="B80" s="37" t="s">
         <v>133</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D80" s="7"/>
       <c r="E80" s="7"/>
-      <c r="F80" s="23"/>
-      <c r="H80" s="29"/>
-      <c r="I80" s="30"/>
-      <c r="J80" s="33"/>
-      <c r="K80" s="32"/>
+      <c r="F80" s="22"/>
+      <c r="H80" s="28"/>
+      <c r="I80" s="29"/>
+      <c r="J80" s="32"/>
+      <c r="K80" s="31"/>
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B81" s="38" t="s">
+      <c r="B81" s="37" t="s">
         <v>134</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D81" s="7"/>
       <c r="E81" s="7"/>
-      <c r="F81" s="23"/>
-      <c r="H81" s="29"/>
-      <c r="I81" s="30"/>
-      <c r="J81" s="33"/>
-      <c r="K81" s="32"/>
+      <c r="F81" s="22"/>
+      <c r="H81" s="28"/>
+      <c r="I81" s="29"/>
+      <c r="J81" s="32"/>
+      <c r="K81" s="31"/>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B82" s="38" t="s">
+      <c r="B82" s="37" t="s">
         <v>135</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D82" s="7"/>
       <c r="E82" s="7"/>
-      <c r="F82" s="23"/>
-      <c r="H82" s="29"/>
-      <c r="I82" s="30"/>
-      <c r="J82" s="33"/>
-      <c r="K82" s="32"/>
+      <c r="F82" s="22"/>
+      <c r="H82" s="28"/>
+      <c r="I82" s="29"/>
+      <c r="J82" s="32"/>
+      <c r="K82" s="31"/>
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B83" s="38" t="s">
+      <c r="B83" s="37" t="s">
         <v>136</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D83" s="7"/>
       <c r="E83" s="7"/>
-      <c r="F83" s="23"/>
-      <c r="H83" s="29"/>
-      <c r="I83" s="30"/>
-      <c r="J83" s="33"/>
-      <c r="K83" s="32"/>
+      <c r="F83" s="22"/>
+      <c r="H83" s="28"/>
+      <c r="I83" s="29"/>
+      <c r="J83" s="32"/>
+      <c r="K83" s="31"/>
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B84" s="38" t="s">
+      <c r="B84" s="37" t="s">
         <v>137</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D84" s="7"/>
       <c r="E84" s="7"/>
-      <c r="F84" s="23"/>
-      <c r="H84" s="29"/>
-      <c r="I84" s="30"/>
-      <c r="J84" s="33"/>
-      <c r="K84" s="32"/>
+      <c r="F84" s="22"/>
+      <c r="H84" s="28"/>
+      <c r="I84" s="29"/>
+      <c r="J84" s="32"/>
+      <c r="K84" s="31"/>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B85" s="38" t="s">
+      <c r="B85" s="37" t="s">
         <v>138</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D85" s="7"/>
       <c r="E85" s="7"/>
-      <c r="F85" s="23"/>
-      <c r="H85" s="29"/>
-      <c r="I85" s="30"/>
-      <c r="J85" s="33"/>
-      <c r="K85" s="32"/>
+      <c r="F85" s="22"/>
+      <c r="H85" s="28"/>
+      <c r="I85" s="29"/>
+      <c r="J85" s="32"/>
+      <c r="K85" s="31"/>
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B86" s="38" t="s">
+      <c r="B86" s="37" t="s">
         <v>139</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D86" s="7"/>
       <c r="E86" s="7"/>
-      <c r="F86" s="23"/>
-      <c r="H86" s="29"/>
-      <c r="I86" s="30"/>
-      <c r="J86" s="33"/>
-      <c r="K86" s="32"/>
+      <c r="F86" s="22"/>
+      <c r="H86" s="28"/>
+      <c r="I86" s="29"/>
+      <c r="J86" s="32"/>
+      <c r="K86" s="31"/>
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B87" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="23"/>
-      <c r="H87" s="29"/>
-      <c r="I87" s="30"/>
-      <c r="J87" s="33"/>
-      <c r="K87" s="32"/>
-    </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="E88" s="37"/>
+      <c r="E87" s="36"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C24:BE31 BF24:BH29">
+  <conditionalFormatting sqref="C23:BE30 BF23:BH28">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-30000"/>
@@ -4752,6 +4698,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EA932CB685C16745937F9E47466E6AB2" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8c369b4a2c9ad3a6a15d4404f8d28d07">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b13bd7b7-0283-4ef3-a757-31c1f732bd10" xmlns:ns3="23b33c3d-3246-4d3f-be29-d9e1f59f3609" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fd31e05f9dcbad54842db47ecc1f6296" ns2:_="" ns3:_="">
     <xsd:import namespace="b13bd7b7-0283-4ef3-a757-31c1f732bd10"/>
@@ -4952,15 +4907,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4973,6 +4919,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DB8125D-6372-4976-8818-4518FAEB5203}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EDD9327-21A8-4285-838C-FB2C8FDF8E31}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4991,14 +4945,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DB8125D-6372-4976-8818-4518FAEB5203}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E4EAED3-A0D0-49D1-8418-8D283D8330A2}">
   <ds:schemaRefs>
